--- a/src/tests/fixtures/biody_synthetic.xlsx
+++ b/src/tests/fixtures/biody_synthetic.xlsx
@@ -1525,67 +1525,67 @@
         <v>35</v>
       </c>
       <c r="J2">
-        <v>388</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
         <v>184</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="N2">
-        <v>56</v>
+        <v>520</v>
       </c>
       <c r="O2">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="Q2">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="R2">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="S2">
-        <v>241</v>
+        <v>91</v>
       </c>
       <c r="T2">
-        <v>278</v>
+        <v>38</v>
       </c>
       <c r="U2">
-        <v>315</v>
+        <v>75</v>
       </c>
       <c r="V2">
-        <v>352</v>
+        <v>22</v>
       </c>
       <c r="W2">
-        <v>389</v>
+        <v>59</v>
       </c>
       <c r="X2">
-        <v>426</v>
+        <v>6</v>
       </c>
       <c r="Y2">
-        <v>463</v>
+        <v>43</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AA2">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="AB2">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="AC2">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="AE2">
-        <v>205</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>464</v>
+        <v>24.5</v>
       </c>
       <c r="AM2">
         <v>21</v>
@@ -1594,115 +1594,115 @@
         <v>58</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="AP2">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="AQ2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AR2">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>243</v>
+        <v>63</v>
       </c>
       <c r="AT2">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="AU2">
-        <v>317</v>
+        <v>47</v>
       </c>
       <c r="AV2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AW2">
-        <v>391</v>
+        <v>31</v>
       </c>
       <c r="AX2">
-        <v>428</v>
+        <v>68</v>
       </c>
       <c r="AY2">
-        <v>465</v>
+        <v>15</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="BA2">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="BB2">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="BC2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="BD2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="BE2">
-        <v>207</v>
+        <v>57</v>
       </c>
       <c r="BF2">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="BG2">
-        <v>281</v>
+        <v>41</v>
       </c>
       <c r="BH2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="BI2">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="BJ2">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="BK2">
-        <v>429</v>
+        <v>9</v>
       </c>
       <c r="BL2">
-        <v>466</v>
+        <v>46</v>
       </c>
       <c r="BM2">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="BN2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BO2">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="BP2">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="BR2">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="BS2">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="BT2">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="BU2">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="BV2">
-        <v>356</v>
+        <v>56</v>
       </c>
       <c r="BW2">
-        <v>393</v>
+        <v>93</v>
       </c>
       <c r="BX2">
-        <v>430</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="BZ2">
         <v>24</v>
@@ -1711,115 +1711,115 @@
         <v>61</v>
       </c>
       <c r="CB2">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="CC2">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="CD2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="CE2">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="CF2">
-        <v>246</v>
+        <v>66</v>
       </c>
       <c r="CG2">
-        <v>283</v>
+        <v>13</v>
       </c>
       <c r="CH2">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="CI2">
-        <v>357</v>
+        <v>87</v>
       </c>
       <c r="CJ2">
-        <v>394</v>
+        <v>34</v>
       </c>
       <c r="CK2">
-        <v>431</v>
+        <v>71</v>
       </c>
       <c r="CL2">
-        <v>468</v>
+        <v>18</v>
       </c>
       <c r="CM2">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="CN2">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="CO2">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="CP2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="CQ2">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="CR2">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="CS2">
-        <v>247</v>
+        <v>7</v>
       </c>
       <c r="CT2">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="CU2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="CV2">
-        <v>358</v>
+        <v>28</v>
       </c>
       <c r="CW2">
-        <v>395</v>
+        <v>65</v>
       </c>
       <c r="CX2">
-        <v>432</v>
+        <v>12</v>
       </c>
       <c r="CY2">
-        <v>469</v>
+        <v>49</v>
       </c>
       <c r="CZ2">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="DA2">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="DB2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DC2">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="DD2">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="DE2">
-        <v>211</v>
+        <v>91</v>
       </c>
       <c r="DF2">
-        <v>248</v>
+        <v>38</v>
       </c>
       <c r="DG2">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="DH2">
-        <v>322</v>
+        <v>22</v>
       </c>
       <c r="DI2">
-        <v>359</v>
+        <v>59</v>
       </c>
       <c r="DJ2">
-        <v>396</v>
+        <v>6</v>
       </c>
       <c r="DK2">
-        <v>433</v>
+        <v>43</v>
       </c>
       <c r="DL2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="DM2">
         <v>27</v>
@@ -1828,142 +1828,142 @@
         <v>64</v>
       </c>
       <c r="DO2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="DP2">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="DQ2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="DR2">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="DS2">
-        <v>249</v>
+        <v>69</v>
       </c>
       <c r="DT2">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c r="DU2">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="DV2">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="DW2">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="DX2">
-        <v>434</v>
+        <v>74</v>
       </c>
       <c r="DY2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="DZ2">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="EA2">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="EB2">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="EC2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="ED2">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="EE2">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="EF2">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="EG2">
-        <v>287</v>
+        <v>47</v>
       </c>
       <c r="EH2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="EI2">
-        <v>361</v>
+        <v>31</v>
       </c>
       <c r="EJ2">
-        <v>398</v>
+        <v>68</v>
       </c>
       <c r="EK2">
-        <v>435</v>
+        <v>15</v>
       </c>
       <c r="EL2">
-        <v>472</v>
+        <v>52</v>
       </c>
       <c r="EM2">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="EN2">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="EO2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="EP2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="EQ2">
-        <v>177</v>
+        <v>57</v>
       </c>
       <c r="ES2">
-        <v>251</v>
+        <v>41</v>
       </c>
       <c r="ET2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="EU2">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="EV2">
-        <v>362</v>
+        <v>62</v>
       </c>
       <c r="EW2">
-        <v>399</v>
+        <v>9</v>
       </c>
       <c r="EX2">
-        <v>436</v>
+        <v>46</v>
       </c>
       <c r="EY2">
-        <v>473</v>
+        <v>83</v>
       </c>
       <c r="EZ2">
         <v>30</v>
       </c>
       <c r="FB2">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="FC2">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="FF2">
-        <v>252</v>
+        <v>72</v>
       </c>
       <c r="FI2">
-        <v>363</v>
+        <v>93</v>
       </c>
       <c r="FL2">
-        <v>474</v>
+        <v>24</v>
       </c>
       <c r="FM2">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="FN2">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="FO2">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="FP2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="FR2" t="s">
         <v>184</v>

--- a/src/tests/fixtures/biody_synthetic.xlsx
+++ b/src/tests/fixtures/biody_synthetic.xlsx
@@ -1584,6 +1584,12 @@
       <c r="AE2">
         <v>85</v>
       </c>
+      <c r="AG2">
+        <v>100</v>
+      </c>
+      <c r="AH2">
+        <v>90</v>
+      </c>
       <c r="AL2">
         <v>24.5</v>
       </c>
